--- a/dist/授权码列表_v1.8.0.xlsx
+++ b/dist/授权码列表_v1.8.0.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="216">
   <si>
     <t>序号</t>
   </si>
@@ -57,10 +57,13 @@
     <t>DAB9-A420-F424</t>
   </si>
   <si>
+    <t>马</t>
+  </si>
+  <si>
+    <t>1984-D690-8CD1</t>
+  </si>
+  <si>
     <t>曾</t>
-  </si>
-  <si>
-    <t>1984-D690-8CD1</t>
   </si>
   <si>
     <t>E98A-025F-C1D8</t>
@@ -685,7 +688,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,13 +715,6 @@
       <color rgb="FF006600"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1195,148 +1191,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1767,7 +1763,9 @@
       <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="14.5" spans="1:5">
@@ -1775,7 +1773,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -1788,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>6</v>
@@ -1801,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>6</v>
@@ -1814,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>6</v>
@@ -1827,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>6</v>
@@ -1840,7 +1838,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>6</v>
@@ -1853,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>6</v>
@@ -1866,7 +1864,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>6</v>
@@ -1879,7 +1877,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>6</v>
@@ -1892,7 +1890,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>6</v>
@@ -1905,7 +1903,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>6</v>
@@ -1918,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>6</v>
@@ -1931,7 +1929,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>6</v>
@@ -1944,7 +1942,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>6</v>
@@ -1957,7 +1955,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>6</v>
@@ -1970,7 +1968,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -1983,7 +1981,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>6</v>
@@ -1996,7 +1994,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>6</v>
@@ -2009,7 +2007,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>6</v>
@@ -2022,7 +2020,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>6</v>
@@ -2035,7 +2033,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>6</v>
@@ -2048,7 +2046,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>6</v>
@@ -2061,7 +2059,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>6</v>
@@ -2074,7 +2072,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>6</v>
@@ -2087,7 +2085,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>6</v>
@@ -2100,7 +2098,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>6</v>
@@ -2113,7 +2111,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>6</v>
@@ -2126,7 +2124,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>6</v>
@@ -2139,7 +2137,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>6</v>
@@ -2152,7 +2150,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>6</v>
@@ -2165,7 +2163,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>6</v>
@@ -2178,7 +2176,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>6</v>
@@ -2191,7 +2189,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>6</v>
@@ -2204,7 +2202,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>6</v>
@@ -2217,7 +2215,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>6</v>
@@ -2230,7 +2228,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>6</v>
@@ -2243,7 +2241,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>6</v>
@@ -2256,7 +2254,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>6</v>
@@ -2269,7 +2267,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>6</v>
@@ -2282,7 +2280,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>6</v>
@@ -2295,7 +2293,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>6</v>
@@ -2308,7 +2306,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>6</v>
@@ -2321,7 +2319,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>6</v>
@@ -2334,7 +2332,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>6</v>
@@ -2347,7 +2345,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>6</v>
@@ -2360,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>6</v>
@@ -2373,7 +2371,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>6</v>
@@ -2386,7 +2384,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>6</v>
@@ -2399,7 +2397,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>6</v>
@@ -2412,7 +2410,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>6</v>
@@ -2425,7 +2423,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -2438,7 +2436,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>6</v>
@@ -2451,7 +2449,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>6</v>
@@ -2464,7 +2462,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
@@ -2477,7 +2475,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>6</v>
@@ -2490,7 +2488,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>6</v>
@@ -2503,7 +2501,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
@@ -2516,7 +2514,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>6</v>
@@ -2529,7 +2527,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>6</v>
@@ -2542,7 +2540,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>6</v>
@@ -2555,7 +2553,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>6</v>
@@ -2568,7 +2566,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>6</v>
@@ -2581,7 +2579,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>6</v>
@@ -2594,7 +2592,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>6</v>
@@ -2607,7 +2605,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>6</v>
@@ -2620,7 +2618,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>6</v>
@@ -2633,7 +2631,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>6</v>
@@ -2646,7 +2644,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>6</v>
@@ -2659,7 +2657,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>6</v>
@@ -2672,7 +2670,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>6</v>
@@ -2685,7 +2683,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>6</v>
@@ -2698,7 +2696,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>6</v>
@@ -2711,7 +2709,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>6</v>
@@ -2724,7 +2722,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>6</v>
@@ -2737,7 +2735,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>6</v>
@@ -2750,7 +2748,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>6</v>
@@ -2763,7 +2761,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>6</v>
@@ -2776,7 +2774,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>6</v>
@@ -2789,7 +2787,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>6</v>
@@ -2802,7 +2800,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>6</v>
@@ -2815,7 +2813,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>6</v>
@@ -2828,7 +2826,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>6</v>
@@ -2841,7 +2839,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>6</v>
@@ -2854,7 +2852,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>6</v>
@@ -2867,7 +2865,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>6</v>
@@ -2880,7 +2878,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>6</v>
@@ -2893,7 +2891,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>6</v>
@@ -2906,7 +2904,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>6</v>
@@ -2919,7 +2917,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>6</v>
@@ -2932,7 +2930,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>6</v>
@@ -2945,7 +2943,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>6</v>
@@ -2958,7 +2956,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>6</v>
@@ -2971,7 +2969,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>6</v>
@@ -2984,7 +2982,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>6</v>
@@ -2997,7 +2995,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>6</v>
@@ -3010,7 +3008,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>6</v>
@@ -3023,7 +3021,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>6</v>
@@ -3036,7 +3034,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>6</v>
@@ -3049,7 +3047,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>6</v>
@@ -3062,7 +3060,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>6</v>
@@ -3075,7 +3073,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>6</v>
@@ -3088,7 +3086,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>6</v>
@@ -3101,7 +3099,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>6</v>
@@ -3114,7 +3112,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>6</v>
@@ -3127,7 +3125,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>6</v>
@@ -3140,7 +3138,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>6</v>
@@ -3153,7 +3151,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>6</v>
@@ -3166,7 +3164,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>6</v>
@@ -3179,7 +3177,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>6</v>
@@ -3192,7 +3190,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>6</v>
@@ -3205,7 +3203,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>6</v>
@@ -3218,7 +3216,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>6</v>
@@ -3231,7 +3229,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>6</v>
@@ -3244,7 +3242,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>6</v>
@@ -3257,7 +3255,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>6</v>
@@ -3270,7 +3268,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>6</v>
@@ -3283,7 +3281,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>6</v>
@@ -3296,7 +3294,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>6</v>
@@ -3309,7 +3307,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>6</v>
@@ -3322,7 +3320,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>6</v>
@@ -3335,7 +3333,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>6</v>
@@ -3348,7 +3346,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>6</v>
@@ -3361,7 +3359,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>6</v>
@@ -3374,7 +3372,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>6</v>
@@ -3387,7 +3385,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>6</v>
@@ -3400,7 +3398,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>6</v>
@@ -3413,7 +3411,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>6</v>
@@ -3426,7 +3424,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>6</v>
@@ -3439,7 +3437,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>6</v>
@@ -3452,7 +3450,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>6</v>
@@ -3465,7 +3463,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>6</v>
@@ -3478,7 +3476,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>6</v>
@@ -3491,7 +3489,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>6</v>
@@ -3504,7 +3502,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>6</v>
@@ -3517,7 +3515,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>6</v>
@@ -3530,7 +3528,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>6</v>
@@ -3543,7 +3541,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>6</v>
@@ -3556,7 +3554,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>6</v>
@@ -3569,7 +3567,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>6</v>
@@ -3582,7 +3580,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>6</v>
@@ -3595,7 +3593,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>6</v>
@@ -3608,7 +3606,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>6</v>
@@ -3621,7 +3619,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>6</v>
@@ -3634,7 +3632,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>6</v>
@@ -3647,7 +3645,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>6</v>
@@ -3660,7 +3658,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>6</v>
@@ -3673,7 +3671,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>6</v>
@@ -3686,7 +3684,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>6</v>
@@ -3699,7 +3697,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>6</v>
@@ -3712,7 +3710,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>6</v>
@@ -3725,7 +3723,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>6</v>
@@ -3738,7 +3736,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>6</v>
@@ -3751,7 +3749,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>6</v>
@@ -3764,7 +3762,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>6</v>
@@ -3777,7 +3775,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>6</v>
@@ -3790,7 +3788,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>6</v>
@@ -3803,7 +3801,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>6</v>
@@ -3816,7 +3814,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>6</v>
@@ -3829,7 +3827,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>6</v>
@@ -3842,7 +3840,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>6</v>
@@ -3855,7 +3853,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>6</v>
@@ -3868,7 +3866,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>6</v>
@@ -3881,7 +3879,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>6</v>
@@ -3894,7 +3892,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>6</v>
@@ -3907,7 +3905,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>6</v>
@@ -3920,7 +3918,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>6</v>
@@ -3933,7 +3931,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>6</v>
@@ -3946,7 +3944,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>6</v>
@@ -3959,7 +3957,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>6</v>
@@ -3972,7 +3970,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>6</v>
@@ -3985,7 +3983,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>6</v>
@@ -3998,7 +3996,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>6</v>
@@ -4011,7 +4009,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>6</v>
@@ -4024,7 +4022,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>6</v>
@@ -4037,7 +4035,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>6</v>
@@ -4050,7 +4048,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>6</v>
@@ -4063,7 +4061,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>6</v>
@@ -4076,7 +4074,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>6</v>
@@ -4089,7 +4087,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>6</v>
@@ -4102,7 +4100,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>6</v>
@@ -4115,7 +4113,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>6</v>
@@ -4128,7 +4126,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>6</v>
@@ -4141,7 +4139,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>6</v>
@@ -4154,7 +4152,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>6</v>
@@ -4167,7 +4165,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>6</v>
@@ -4180,7 +4178,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>6</v>
@@ -4193,7 +4191,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>6</v>
@@ -4206,7 +4204,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>6</v>
@@ -4219,7 +4217,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>6</v>
@@ -4232,7 +4230,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>6</v>
@@ -4245,7 +4243,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>6</v>
@@ -4258,7 +4256,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>6</v>
@@ -4271,7 +4269,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>6</v>
@@ -4284,7 +4282,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>6</v>
@@ -4297,7 +4295,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>6</v>
@@ -4310,7 +4308,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>6</v>
@@ -4323,7 +4321,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>6</v>
@@ -4348,37 +4346,37 @@
   <sheetData>
     <row r="1" ht="17.5" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/dist/授权码列表_v1.8.0.xlsx
+++ b/dist/授权码列表_v1.8.0.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="217">
   <si>
     <t>序号</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>E98A-025F-C1D8</t>
+  </si>
+  <si>
+    <t>何</t>
   </si>
   <si>
     <t>E216-DB66-F833</t>
@@ -1778,7 +1781,9 @@
       <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="14.5" spans="1:5">
@@ -1786,7 +1791,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>6</v>
@@ -1799,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>6</v>
@@ -1812,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>6</v>
@@ -1825,7 +1830,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>6</v>
@@ -1838,7 +1843,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>6</v>
@@ -1851,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>6</v>
@@ -1864,7 +1869,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>6</v>
@@ -1877,7 +1882,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>6</v>
@@ -1890,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>6</v>
@@ -1903,7 +1908,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>6</v>
@@ -1916,7 +1921,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>6</v>
@@ -1929,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>6</v>
@@ -1942,7 +1947,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>6</v>
@@ -1955,7 +1960,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>6</v>
@@ -1968,7 +1973,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -1981,7 +1986,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>6</v>
@@ -1994,7 +1999,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>6</v>
@@ -2007,7 +2012,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>6</v>
@@ -2020,7 +2025,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>6</v>
@@ -2033,7 +2038,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>6</v>
@@ -2046,7 +2051,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>6</v>
@@ -2059,7 +2064,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>6</v>
@@ -2072,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>6</v>
@@ -2085,7 +2090,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>6</v>
@@ -2098,7 +2103,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>6</v>
@@ -2111,7 +2116,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>6</v>
@@ -2124,7 +2129,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>6</v>
@@ -2137,7 +2142,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>6</v>
@@ -2150,7 +2155,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>6</v>
@@ -2163,7 +2168,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>6</v>
@@ -2176,7 +2181,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>6</v>
@@ -2189,7 +2194,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>6</v>
@@ -2202,7 +2207,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>6</v>
@@ -2215,7 +2220,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>6</v>
@@ -2228,7 +2233,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>6</v>
@@ -2241,7 +2246,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>6</v>
@@ -2254,7 +2259,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>6</v>
@@ -2267,7 +2272,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>6</v>
@@ -2280,7 +2285,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>6</v>
@@ -2293,7 +2298,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>6</v>
@@ -2306,7 +2311,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>6</v>
@@ -2319,7 +2324,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>6</v>
@@ -2332,7 +2337,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>6</v>
@@ -2345,7 +2350,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>6</v>
@@ -2358,7 +2363,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>6</v>
@@ -2371,7 +2376,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>6</v>
@@ -2384,7 +2389,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>6</v>
@@ -2397,7 +2402,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>6</v>
@@ -2410,7 +2415,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>6</v>
@@ -2423,7 +2428,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -2436,7 +2441,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>6</v>
@@ -2449,7 +2454,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>6</v>
@@ -2462,7 +2467,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
@@ -2475,7 +2480,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>6</v>
@@ -2488,7 +2493,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>6</v>
@@ -2501,7 +2506,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
@@ -2514,7 +2519,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>6</v>
@@ -2527,7 +2532,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>6</v>
@@ -2540,7 +2545,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>6</v>
@@ -2553,7 +2558,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>6</v>
@@ -2566,7 +2571,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>6</v>
@@ -2579,7 +2584,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>6</v>
@@ -2592,7 +2597,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>6</v>
@@ -2605,7 +2610,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>6</v>
@@ -2618,7 +2623,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>6</v>
@@ -2631,7 +2636,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>6</v>
@@ -2644,7 +2649,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>6</v>
@@ -2657,7 +2662,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>6</v>
@@ -2670,7 +2675,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>6</v>
@@ -2683,7 +2688,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>6</v>
@@ -2696,7 +2701,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>6</v>
@@ -2709,7 +2714,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>6</v>
@@ -2722,7 +2727,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>6</v>
@@ -2735,7 +2740,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>6</v>
@@ -2748,7 +2753,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>6</v>
@@ -2761,7 +2766,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>6</v>
@@ -2774,7 +2779,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>6</v>
@@ -2787,7 +2792,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>6</v>
@@ -2800,7 +2805,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>6</v>
@@ -2813,7 +2818,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>6</v>
@@ -2826,7 +2831,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>6</v>
@@ -2839,7 +2844,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>6</v>
@@ -2852,7 +2857,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>6</v>
@@ -2865,7 +2870,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>6</v>
@@ -2878,7 +2883,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>6</v>
@@ -2891,7 +2896,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>6</v>
@@ -2904,7 +2909,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>6</v>
@@ -2917,7 +2922,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>6</v>
@@ -2930,7 +2935,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>6</v>
@@ -2943,7 +2948,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>6</v>
@@ -2956,7 +2961,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>6</v>
@@ -2969,7 +2974,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>6</v>
@@ -2982,7 +2987,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>6</v>
@@ -2995,7 +3000,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>6</v>
@@ -3008,7 +3013,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>6</v>
@@ -3021,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>6</v>
@@ -3034,7 +3039,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>6</v>
@@ -3047,7 +3052,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>6</v>
@@ -3060,7 +3065,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>6</v>
@@ -3073,7 +3078,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>6</v>
@@ -3086,7 +3091,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>6</v>
@@ -3099,7 +3104,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>6</v>
@@ -3112,7 +3117,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>6</v>
@@ -3125,7 +3130,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>6</v>
@@ -3138,7 +3143,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>6</v>
@@ -3151,7 +3156,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>6</v>
@@ -3164,7 +3169,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>6</v>
@@ -3177,7 +3182,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>6</v>
@@ -3190,7 +3195,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>6</v>
@@ -3203,7 +3208,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>6</v>
@@ -3216,7 +3221,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>6</v>
@@ -3229,7 +3234,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>6</v>
@@ -3242,7 +3247,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>6</v>
@@ -3255,7 +3260,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>6</v>
@@ -3268,7 +3273,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>6</v>
@@ -3281,7 +3286,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>6</v>
@@ -3294,7 +3299,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>6</v>
@@ -3307,7 +3312,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>6</v>
@@ -3320,7 +3325,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>6</v>
@@ -3333,7 +3338,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>6</v>
@@ -3346,7 +3351,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>6</v>
@@ -3359,7 +3364,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>6</v>
@@ -3372,7 +3377,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>6</v>
@@ -3385,7 +3390,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>6</v>
@@ -3398,7 +3403,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>6</v>
@@ -3411,7 +3416,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>6</v>
@@ -3424,7 +3429,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>6</v>
@@ -3437,7 +3442,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>6</v>
@@ -3450,7 +3455,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>6</v>
@@ -3463,7 +3468,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>6</v>
@@ -3476,7 +3481,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>6</v>
@@ -3489,7 +3494,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>6</v>
@@ -3502,7 +3507,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>6</v>
@@ -3515,7 +3520,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>6</v>
@@ -3528,7 +3533,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>6</v>
@@ -3541,7 +3546,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>6</v>
@@ -3554,7 +3559,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>6</v>
@@ -3567,7 +3572,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>6</v>
@@ -3580,7 +3585,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>6</v>
@@ -3593,7 +3598,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>6</v>
@@ -3606,7 +3611,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>6</v>
@@ -3619,7 +3624,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>6</v>
@@ -3632,7 +3637,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>6</v>
@@ -3645,7 +3650,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>6</v>
@@ -3658,7 +3663,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>6</v>
@@ -3671,7 +3676,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>6</v>
@@ -3684,7 +3689,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>6</v>
@@ -3697,7 +3702,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>6</v>
@@ -3710,7 +3715,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>6</v>
@@ -3723,7 +3728,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>6</v>
@@ -3736,7 +3741,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>6</v>
@@ -3749,7 +3754,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>6</v>
@@ -3762,7 +3767,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>6</v>
@@ -3775,7 +3780,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>6</v>
@@ -3788,7 +3793,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>6</v>
@@ -3801,7 +3806,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>6</v>
@@ -3814,7 +3819,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>6</v>
@@ -3827,7 +3832,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>6</v>
@@ -3840,7 +3845,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>6</v>
@@ -3853,7 +3858,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>6</v>
@@ -3866,7 +3871,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>6</v>
@@ -3879,7 +3884,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>6</v>
@@ -3892,7 +3897,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>6</v>
@@ -3905,7 +3910,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>6</v>
@@ -3918,7 +3923,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>6</v>
@@ -3931,7 +3936,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>6</v>
@@ -3944,7 +3949,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>6</v>
@@ -3957,7 +3962,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>6</v>
@@ -3970,7 +3975,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>6</v>
@@ -3983,7 +3988,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>6</v>
@@ -3996,7 +4001,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>6</v>
@@ -4009,7 +4014,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>6</v>
@@ -4022,7 +4027,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>6</v>
@@ -4035,7 +4040,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>6</v>
@@ -4048,7 +4053,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>6</v>
@@ -4061,7 +4066,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>6</v>
@@ -4074,7 +4079,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>6</v>
@@ -4087,7 +4092,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>6</v>
@@ -4100,7 +4105,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>6</v>
@@ -4113,7 +4118,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>6</v>
@@ -4126,7 +4131,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>6</v>
@@ -4139,7 +4144,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>6</v>
@@ -4152,7 +4157,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>6</v>
@@ -4165,7 +4170,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>6</v>
@@ -4178,7 +4183,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>6</v>
@@ -4191,7 +4196,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>6</v>
@@ -4204,7 +4209,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>6</v>
@@ -4217,7 +4222,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>6</v>
@@ -4230,7 +4235,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>6</v>
@@ -4243,7 +4248,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>6</v>
@@ -4256,7 +4261,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>6</v>
@@ -4269,7 +4274,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>6</v>
@@ -4282,7 +4287,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>6</v>
@@ -4295,7 +4300,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>6</v>
@@ -4308,7 +4313,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>6</v>
@@ -4321,7 +4326,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>6</v>
@@ -4346,37 +4351,37 @@
   <sheetData>
     <row r="1" ht="17.5" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
